--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="432">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -490,7 +490,7 @@
     <t>Allows identification of the charge Item as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
-    <t>1837: source value from INTEGRATED BILLING ACTION - AR BILL NUMBER (350-.11)</t>
+    <t>1837: source value based on INTEGRATED BILLING ACTION - AR BILL NUMBER (350-.11)</t>
   </si>
   <si>
     <t>IB.IBAction.ARBillNumber</t>
@@ -724,7 +724,11 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>2029: source value from INTEGRATED BILLING ACTION - CANCELLATION REASON (350-.1) case NOT NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+dpci-27-2029:If NOT NULL then source value from (350-.1) {null}</t>
+  </si>
+  <si>
+    <t>2029: source value based on INTEGRATED BILLING ACTION - CANCELLATION REASON (350-.1) if NOT NULL</t>
   </si>
   <si>
     <t>IB.IBAction.IBChargeRemoveReasonIEN</t>
@@ -756,7 +760,7 @@
     <t>Links the event to the Patient context.</t>
   </si>
   <si>
-    <t>1839: reference from INTEGRATED BILLING ACTION - PATIENT &gt; PATIENT (350-.02 &gt; 2-)</t>
+    <t>1839: reference based on INTEGRATED BILLING ACTION - PATIENT &gt; PATIENT (350-.02 &gt; 2-)</t>
   </si>
   <si>
     <t>IB.IBAction.PatientIEN</t>
@@ -795,10 +799,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpci-27-2008:360-1.02 &gt; 399-304&gt;399.0304-20&gt;409.68-.05: if Outpatient then /EncounterOutpatient {null}dpci-27-2009:360-1.02 &gt; 399-.08: if Inpatient then /EncounterInpatientEncounter {null}</t>
-  </si>
-  <si>
-    <t>2009: reference from IB-FB INTERFACE TRACKING - BILL/CLAIMS &gt; BILL/CLAIMS - PTF ENTRY NUMBER (360-1.02 &gt; 399-.08) case Inpatient</t>
+dpci-27-2008:If Outpatient then reference /EncounterOutpatient based on (360-1.02 &gt; 399-304&gt;399.0304-20&gt;409.68-.05) {null}dpci-27-2009:If Inpatient then reference /EncounterInpatientEncounter based on (360-1.02 &gt; 399-.08) {null}</t>
+  </si>
+  <si>
+    <t>2009: reference based on IB-FB INTERFACE TRACKING - BILL/CLAIMS &gt; BILL/CLAIMS - PTF ENTRY NUMBER (360-1.02 &gt; 399-.08) if Inpatient</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -894,7 +898,7 @@
 </t>
   </si>
   <si>
-    <t>1973: source value from INTEGRATED BILLING ACTION - DATE BILLED FROM (350-.14)</t>
+    <t>1973: source value based on INTEGRATED BILLING ACTION - DATE BILLED FROM (350-.14)</t>
   </si>
   <si>
     <t>IB.IBAction.BillFromDateTime</t>
@@ -927,7 +931,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>1974: source value from INTEGRATED BILLING ACTION - DATE BILLED TO (350-.15)</t>
+    <t>1974: source value based on INTEGRATED BILLING ACTION - DATE BILLED TO (350-.15)</t>
   </si>
   <si>
     <t>IB.IBAction.BillToDateTime</t>
@@ -1191,7 +1195,7 @@
     <t>The actual date when the service associated with the charge has been rendered is captured in occurrence[x].</t>
   </si>
   <si>
-    <t>1835: source value from INTEGRATED BILLING ACTION - DATE ENTRY ADDED (350-12)</t>
+    <t>1835: source value based on INTEGRATED BILLING ACTION - DATE ENTRY ADDED (350-12)</t>
   </si>
   <si>
     <t>IB.IBAction.EnteredDateTime</t>
@@ -1260,7 +1264,7 @@
 </t>
   </si>
   <si>
-    <t>2010: reference from PRESCRIPTION - IB NUMBER &gt; INTEGRATED BILLING ACTION (52-106 &gt; 350-)</t>
+    <t>2010: reference based on PRESCRIPTION - IB NUMBER &gt; INTEGRATED BILLING ACTION (52-106 &gt; 350-)</t>
   </si>
   <si>
     <t>ChargeItem.service:va-rxrefill</t>
@@ -1273,7 +1277,7 @@
 </t>
   </si>
   <si>
-    <t>2011: reference from PRESCRIPTION - IB NUMBER &gt; INTEGRATED BILLING ACTION (52-106 &gt; 350-)</t>
+    <t>2011: reference based on PRESCRIPTION - IB NUMBER &gt; INTEGRATED BILLING ACTION (52-106 &gt; 350-)</t>
   </si>
   <si>
     <t>ChargeItem.service:va-rxpartial</t>
@@ -1286,7 +1290,7 @@
 </t>
   </si>
   <si>
-    <t>2012: reference from PRESCRIPTION - IB NUMBER &gt; INTEGRATED BILLING ACTION (52-106 &gt; 350-)</t>
+    <t>2012: reference based on PRESCRIPTION - IB NUMBER &gt; INTEGRATED BILLING ACTION (52-106 &gt; 350-)</t>
   </si>
   <si>
     <t>ChargeItem.product[x]</t>
@@ -1717,7 +1721,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="127.90234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="128.93359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="45.6171875" customWidth="true" bestFit="true"/>
@@ -4106,22 +4110,22 @@
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>227</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -4129,14 +4133,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4155,17 +4159,17 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4214,7 +4218,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>90</v>
@@ -4229,34 +4233,34 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4275,17 +4279,17 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4334,7 +4338,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4346,37 +4350,37 @@
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4395,16 +4399,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4442,7 +4446,7 @@
         <v>79</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4452,7 +4456,7 @@
         <v>210</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4473,30 +4477,30 @@
         <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>162</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4515,16 +4519,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4574,7 +4578,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4595,24 +4599,24 @@
         <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>162</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4727,10 +4731,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4847,10 +4851,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4873,16 +4877,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4932,7 +4936,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4941,25 +4945,25 @@
         <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>79</v>
@@ -4967,10 +4971,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4993,23 +4997,23 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="R28" t="s" s="2">
         <v>79</v>
@@ -5054,7 +5058,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5063,25 +5067,25 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5089,10 +5093,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5115,13 +5119,13 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5172,7 +5176,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5193,13 +5197,13 @@
         <v>79</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5207,10 +5211,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5325,10 +5329,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5445,14 +5449,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5474,10 +5478,10 @@
         <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>139</v>
@@ -5532,7 +5536,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5567,10 +5571,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5596,10 +5600,10 @@
         <v>190</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5629,10 +5633,10 @@
         <v>193</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -5650,7 +5654,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5671,13 +5675,13 @@
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>162</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -5685,10 +5689,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5711,13 +5715,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5768,7 +5772,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>90</v>
@@ -5789,24 +5793,24 @@
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5829,16 +5833,16 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5888,7 +5892,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5909,13 +5913,13 @@
         <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>133</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
@@ -5923,10 +5927,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5949,16 +5953,16 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6008,7 +6012,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6035,7 +6039,7 @@
         <v>133</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
@@ -6043,10 +6047,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6069,16 +6073,16 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6128,7 +6132,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6152,7 +6156,7 @@
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6163,10 +6167,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6189,16 +6193,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6248,7 +6252,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6272,7 +6276,7 @@
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6283,10 +6287,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6312,13 +6316,13 @@
         <v>190</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6347,10 +6351,10 @@
         <v>193</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -6368,7 +6372,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6395,7 +6399,7 @@
         <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -6403,10 +6407,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6429,16 +6433,16 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6488,7 +6492,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6512,7 +6516,7 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6523,10 +6527,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6549,16 +6553,16 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6608,7 +6612,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6632,7 +6636,7 @@
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6643,10 +6647,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6672,13 +6676,13 @@
         <v>201</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6728,7 +6732,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6763,10 +6767,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6789,16 +6793,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6848,7 +6852,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6872,21 +6876,21 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6909,16 +6913,16 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6968,7 +6972,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6983,10 +6987,10 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
@@ -7003,10 +7007,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7032,13 +7036,13 @@
         <v>190</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7067,10 +7071,10 @@
         <v>193</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7088,7 +7092,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7109,24 +7113,24 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7149,13 +7153,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7194,7 +7198,7 @@
         <v>79</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -7204,7 +7208,7 @@
         <v>210</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7225,27 +7229,27 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>79</v>
@@ -7267,13 +7271,13 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7324,7 +7328,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7339,33 +7343,33 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>79</v>
@@ -7387,13 +7391,13 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7444,7 +7448,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7459,33 +7463,33 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>79</v>
@@ -7507,13 +7511,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7564,7 +7568,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7579,30 +7583,30 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7625,13 +7629,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7661,10 +7665,10 @@
         <v>193</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -7682,7 +7686,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7709,7 +7713,7 @@
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>79</v>
@@ -7717,10 +7721,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7743,16 +7747,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7802,7 +7806,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7837,10 +7841,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7863,13 +7867,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7920,7 +7924,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7941,13 +7945,13 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -7955,10 +7959,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7981,13 +7985,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8038,7 +8042,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8059,7 +8063,7 @@
         <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -725,7 +725,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpci-27-2029:If NOT NULL then source value from (350-.1) {null}</t>
+dpci-27-2029:If NOT NULL then source value from (350-.1) {true}</t>
   </si>
   <si>
     <t>2029: source value based on INTEGRATED BILLING ACTION - CANCELLATION REASON (350-.1) if NOT NULL</t>
@@ -799,7 +799,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpci-27-2008:If Outpatient then reference /EncounterOutpatient based on (360-1.02 &gt; 399-304&gt;399.0304-20&gt;409.68-.05) {null}dpci-27-2009:If Inpatient then reference /EncounterInpatientEncounter based on (360-1.02 &gt; 399-.08) {null}</t>
+dpci-27-2008:If Outpatient then reference /EncounterOutpatient based on (360-1.02 &gt; 399-304&gt;399.0304-20&gt;409.68-.05) {true}dpci-27-2009:If Inpatient then reference /EncounterInpatientEncounter based on (360-1.02 &gt; 399-.08) {true}</t>
   </si>
   <si>
     <t>2009: reference based on IB-FB INTERFACE TRACKING - BILL/CLAIMS &gt; BILL/CLAIMS - PTF ENTRY NUMBER (360-1.02 &gt; 399-.08) if Inpatient</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -760,7 +760,7 @@
     <t>Links the event to the Patient context.</t>
   </si>
   <si>
-    <t>1839: reference based on INTEGRATED BILLING ACTION - PATIENT &gt; PATIENT (350-.02 &gt; 2-)</t>
+    <t>1839: reference based on INTEGRATED BILLING ACTION - PATIENT (350-.02)</t>
   </si>
   <si>
     <t>IB.IBAction.PatientIEN</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$55</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="438">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -490,22 +490,51 @@
     <t>Allows identification of the charge Item as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>FT1.2</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>ChargeItem.identifier:va-billno</t>
+  </si>
+  <si>
+    <t>va-billno</t>
+  </si>
+  <si>
     <t>1837: source value based on INTEGRATED BILLING ACTION - AR BILL NUMBER (350-.11)</t>
   </si>
   <si>
     <t>IB.IBAction.ARBillNumber</t>
   </si>
   <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>FT1.2</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
+    <t>ChargeItem.identifier:va-artransno</t>
+  </si>
+  <si>
+    <t>va-artransno</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+dpci-27-2218:If AR TRANSACTION - TRANSACTION TYPE &gt; ACCOUNTS RECEIVABLE TRANS.TYPE - IEN = 1 OR 35 then source value from (350-.12) {true}</t>
+  </si>
+  <si>
+    <t>2218: source value based on INTEGRATED BILLING ACTION - AR TRANSACTION NUMBER (350-.12) if AR TRANSACTION - TRANSACTION TYPE &gt; ACCOUNTS RECEIVABLE TRANS.TYPE - IEN = 1 OR 35</t>
+  </si>
+  <si>
+    <t>IB.IBAction.ARTransactionNumber</t>
   </si>
   <si>
     <t>ChargeItem.definitionUri</t>
@@ -672,9 +701,6 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -724,14 +750,11 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpci-27-2029:If NOT NULL then source value from (350-.1) {true}</t>
-  </si>
-  <si>
-    <t>2029: source value based on INTEGRATED BILLING ACTION - CANCELLATION REASON (350-.1) if NOT NULL</t>
-  </si>
-  <si>
-    <t>IB.IBAction.IBChargeRemoveReasonIEN</t>
+    <t>1836: source value based on INTEGRATED BILLING ACTION - ACTION TYPE &gt; IB ACTION TYPE - CHARGE CATEGORY (350-.03 &gt; 350.1-.03)</t>
+  </si>
+  <si>
+    <t>IB.IBAction.IBActionTypeIEN
+Dim.IBActionType.AccountsReceivableCategory,Dim.IBActionType.ARCategoryIEN</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -1242,10 +1265,6 @@
   </si>
   <si>
     <t>Indicated the rendered service that caused this charge.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:$this}
-</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1683,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP53"/>
+  <dimension ref="A1:AP55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.34375" customWidth="true" bestFit="true"/>
@@ -1721,8 +1740,8 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="128.93359375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="181.6171875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="76.3046875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="45.6171875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="97.8125" customWidth="true" bestFit="true"/>
@@ -2954,7 +2973,7 @@
         <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>79</v>
@@ -3010,16 +3029,14 @@
         <v>79</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>147</v>
@@ -3037,10 +3054,10 @@
         <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>154</v>
@@ -3060,9 +3077,11 @@
         <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>79</v>
       </c>
@@ -3071,28 +3090,30 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>79</v>
       </c>
@@ -3140,7 +3161,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3155,32 +3176,34 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>79</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>79</v>
       </c>
@@ -3189,28 +3212,30 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+      <c r="O13" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>79</v>
       </c>
@@ -3258,7 +3283,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3270,33 +3295,33 @@
         <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>102</v>
+        <v>164</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>79</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3304,32 +3329,30 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3339,7 +3362,7 @@
         <v>79</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>79</v>
@@ -3354,13 +3377,13 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
@@ -3378,13 +3401,13 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>79</v>
@@ -3393,34 +3416,34 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3439,18 +3462,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N15" s="2"/>
-      <c r="O15" t="s" s="2">
-        <v>185</v>
-      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
       </c>
@@ -3498,7 +3519,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3519,13 +3540,13 @@
         <v>79</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>79</v>
@@ -3533,14 +3554,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3550,24 +3571,26 @@
         <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
@@ -3577,7 +3600,7 @@
         <v>79</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>79</v>
@@ -3592,13 +3615,13 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -3616,7 +3639,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>90</v>
@@ -3631,41 +3654,41 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>79</v>
@@ -3677,16 +3700,18 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+      <c r="O17" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
       </c>
@@ -3734,19 +3759,19 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>79</v>
@@ -3755,13 +3780,13 @@
         <v>79</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>79</v>
@@ -3769,21 +3794,21 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>79</v>
@@ -3792,20 +3817,18 @@
         <v>79</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -3830,69 +3853,69 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3903,7 +3926,7 @@
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -3912,23 +3935,19 @@
         <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
@@ -3976,19 +3995,19 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
@@ -4000,10 +4019,10 @@
         <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>79</v>
@@ -4011,46 +4030,44 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>136</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>137</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
@@ -4086,46 +4103,46 @@
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>227</v>
+        <v>141</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>228</v>
+        <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>230</v>
+        <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -4133,24 +4150,24 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>79</v>
@@ -4159,17 +4176,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O21" t="s" s="2">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4218,13 +4237,13 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>79</v>
@@ -4233,34 +4252,34 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>238</v>
+        <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>243</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4279,17 +4298,19 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4338,7 +4359,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4350,47 +4371,47 @@
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>252</v>
+        <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>255</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>79</v>
@@ -4399,18 +4420,18 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
@@ -4446,20 +4467,22 @@
         <v>79</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>90</v>
@@ -4471,36 +4494,34 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>79</v>
+        <v>245</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>162</v>
+        <v>248</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4510,7 +4531,7 @@
         <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>79</v>
@@ -4519,18 +4540,18 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4578,7 +4599,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4590,37 +4611,37 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>257</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>79</v>
+        <v>258</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>162</v>
+        <v>260</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4636,18 +4657,20 @@
         <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>202</v>
+        <v>266</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4684,19 +4707,17 @@
         <v>79</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>204</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4708,7 +4729,7 @@
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
@@ -4717,35 +4738,37 @@
         <v>79</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>205</v>
+        <v>271</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>79</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="D26" t="s" s="2">
-        <v>135</v>
+        <v>264</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>79</v>
@@ -4754,19 +4777,19 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>136</v>
+        <v>275</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>137</v>
+        <v>266</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>207</v>
+        <v>267</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>139</v>
+        <v>268</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4804,31 +4827,31 @@
         <v>79</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>79</v>
@@ -4837,24 +4860,24 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>205</v>
+        <v>271</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>79</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4868,26 +4891,24 @@
         <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>211</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -4936,7 +4957,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>213</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4945,25 +4966,25 @@
         <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>284</v>
+        <v>214</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>79</v>
@@ -4971,50 +4992,48 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>275</v>
+        <v>136</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>287</v>
+        <v>137</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>288</v>
+        <v>216</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>289</v>
+        <v>139</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q28" t="s" s="2">
-        <v>290</v>
-      </c>
+      <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
         <v>79</v>
       </c>
@@ -5046,46 +5065,46 @@
         <v>79</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>219</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>292</v>
+        <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>294</v>
+        <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>295</v>
+        <v>214</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5093,10 +5112,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5107,27 +5126,29 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5176,34 +5197,34 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>79</v>
+        <v>287</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>300</v>
+        <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5211,10 +5232,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5228,29 +5249,33 @@
         <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>201</v>
+        <v>282</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>202</v>
+        <v>294</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q30" s="2"/>
+      <c r="Q30" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="R30" t="s" s="2">
         <v>79</v>
       </c>
@@ -5294,7 +5319,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>204</v>
+        <v>298</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5303,25 +5328,25 @@
         <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>79</v>
+        <v>287</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>205</v>
+        <v>302</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>79</v>
@@ -5329,14 +5354,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5355,17 +5380,15 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>136</v>
+        <v>304</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>137</v>
+        <v>305</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5414,7 +5437,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5426,7 +5449,7 @@
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>79</v>
@@ -5435,13 +5458,13 @@
         <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>79</v>
+        <v>307</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>205</v>
+        <v>309</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -5449,46 +5472,42 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>307</v>
+        <v>211</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
       </c>
@@ -5536,19 +5555,19 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>309</v>
+        <v>213</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>79</v>
@@ -5563,7 +5582,7 @@
         <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>133</v>
+        <v>214</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
@@ -5571,21 +5590,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -5597,15 +5616,17 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>190</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>137</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5630,13 +5651,13 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>193</v>
+        <v>79</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>313</v>
+        <v>79</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>314</v>
+        <v>79</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -5654,19 +5675,19 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>310</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
@@ -5675,13 +5696,13 @@
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>316</v>
+        <v>214</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -5689,42 +5710,46 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>318</v>
+        <v>136</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5772,19 +5797,19 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
@@ -5793,24 +5818,24 @@
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>321</v>
+        <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>301</v>
+        <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>322</v>
+        <v>133</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5833,17 +5858,15 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>325</v>
+        <v>199</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -5868,13 +5891,13 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>79</v>
+        <v>321</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -5892,7 +5915,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5913,13 +5936,13 @@
         <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
@@ -5927,10 +5950,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5938,7 +5961,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>90</v>
@@ -5956,14 +5979,12 @@
         <v>325</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6012,10 +6033,10 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>90</v>
@@ -6033,24 +6054,24 @@
         <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>133</v>
+        <v>308</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>329</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>79</v>
+        <v>330</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6073,16 +6094,16 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6132,7 +6153,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6153,13 +6174,13 @@
         <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>338</v>
+        <v>133</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -6167,10 +6188,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6190,19 +6211,19 @@
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6252,7 +6273,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6276,10 +6297,10 @@
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>344</v>
+        <v>133</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -6287,10 +6308,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6301,7 +6322,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6310,19 +6331,19 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>190</v>
+        <v>332</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6348,13 +6369,13 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>193</v>
+        <v>79</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -6372,13 +6393,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6396,10 +6417,10 @@
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>79</v>
+        <v>345</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>351</v>
+        <v>79</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -6407,10 +6428,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6430,19 +6451,19 @@
         <v>79</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6492,7 +6513,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6516,7 +6537,7 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6527,10 +6548,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6541,7 +6562,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6550,19 +6571,19 @@
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>359</v>
+        <v>199</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6588,13 +6609,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>79</v>
+        <v>357</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6612,13 +6633,13 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>79</v>
@@ -6636,10 +6657,10 @@
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>79</v>
+        <v>358</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>79</v>
@@ -6647,10 +6668,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6673,16 +6694,16 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>201</v>
+        <v>360</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6732,7 +6753,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6756,7 +6777,7 @@
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6767,10 +6788,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6790,19 +6811,19 @@
         <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6852,7 +6873,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6876,21 +6897,21 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>301</v>
+        <v>370</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6904,25 +6925,25 @@
         <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6972,7 +6993,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6987,10 +7008,10 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>377</v>
+        <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
@@ -7007,10 +7028,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7021,7 +7042,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7030,19 +7051,19 @@
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>190</v>
+        <v>376</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7068,13 +7089,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>193</v>
+        <v>79</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>383</v>
+        <v>79</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>384</v>
+        <v>79</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7092,13 +7113,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7113,24 +7134,24 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>385</v>
+        <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>386</v>
+        <v>308</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>387</v>
+        <v>329</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>388</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7141,27 +7162,29 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>390</v>
+        <v>282</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7198,23 +7221,25 @@
         <v>79</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AC46" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
@@ -7223,34 +7248,32 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>79</v>
+        <v>385</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>394</v>
+        <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>386</v>
+        <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>388</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7259,10 +7282,10 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>79</v>
@@ -7271,15 +7294,17 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>398</v>
+        <v>199</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7304,13 +7329,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7328,7 +7353,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7343,34 +7368,32 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>399</v>
+        <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AN47" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>388</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7379,10 +7402,10 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>79</v>
@@ -7391,13 +7414,13 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7436,19 +7459,17 @@
         <v>79</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7463,33 +7484,33 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="AO48" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>388</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>79</v>
@@ -7511,13 +7532,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7568,7 +7589,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7583,32 +7604,34 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="AO49" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>388</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>79</v>
       </c>
@@ -7620,7 +7643,7 @@
         <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>79</v>
@@ -7629,13 +7652,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7662,13 +7685,13 @@
         <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>193</v>
+        <v>79</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -7686,13 +7709,13 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
@@ -7701,32 +7724,34 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>79</v>
+        <v>400</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7735,29 +7760,27 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -7806,7 +7829,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7821,30 +7844,30 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>79</v>
+        <v>413</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>79</v>
+        <v>400</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>79</v>
+        <v>401</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7855,7 +7878,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -7867,13 +7890,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7900,13 +7923,13 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>79</v>
+        <v>418</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>79</v>
+        <v>419</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -7924,13 +7947,13 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
@@ -7945,13 +7968,13 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>424</v>
+        <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -7959,10 +7982,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7982,18 +8005,20 @@
         <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8042,7 +8067,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8063,20 +8088,256 @@
         <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AN53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP53" t="s" s="2">
+      <c r="AO54" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP53">
+  <autoFilter ref="A1:AP55">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8086,7 +8347,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI52">
+  <conditionalFormatting sqref="A2:AI54">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="441">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -822,10 +822,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpci-27-2008:If Outpatient then reference /EncounterOutpatient based on (360-1.02 &gt; 399-304&gt;399.0304-20&gt;409.68-.05) {true}dpci-27-2009:If Inpatient then reference /EncounterInpatientEncounter based on (360-1.02 &gt; 399-.08) {true}</t>
-  </si>
-  <si>
-    <t>2009: reference based on IB-FB INTERFACE TRACKING - BILL/CLAIMS &gt; BILL/CLAIMS - PTF ENTRY NUMBER (360-1.02 &gt; 399-.08) if Inpatient</t>
+dpci-27-2008:If 360-1.04 == 350 &amp;&amp; Outpatient then reference /EncounterOutpatient based on (360-1.02 &gt; 399-304&gt;399.0304-20&gt;409.68-.05) {true}dpci-27-2009:If 360-1.04 == 350 &amp;&amp; Inpatient then reference /EncounterInpatientEncounter based on (360-1.02 &gt; 399-.08) {true}</t>
+  </si>
+  <si>
+    <t>2009: reference based on IB-FB INTERFACE TRACKING - BILL/CLAIMS &gt; BILL/CLAIMS - PTF ENTRY NUMBER (360-1.02 &gt; 399-.08) if 360-1.04 == 350 &amp;&amp; Inpatient</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1283,7 +1283,11 @@
 </t>
   </si>
   <si>
-    <t>2010: reference based on PRESCRIPTION - IB NUMBER &gt; INTEGRATED BILLING ACTION (52-106 &gt; 350-)</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+dpci-27-2010:If 52-106 == 350 then reference /MedicationDispenseOriginal based on (52-) {true}</t>
+  </si>
+  <si>
+    <t>2010: reference based on PRESCRIPTION - (52-) if 52-106 == 350</t>
   </si>
   <si>
     <t>ChargeItem.service:va-rxrefill</t>
@@ -1296,7 +1300,11 @@
 </t>
   </si>
   <si>
-    <t>2011: reference based on PRESCRIPTION - IB NUMBER &gt; INTEGRATED BILLING ACTION (52-106 &gt; 350-)</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+dpci-27-2011:If 52-106 == 350 then reference /MedicationDispenseRefill based on (52-) {true}</t>
+  </si>
+  <si>
+    <t>2011: reference based on PRESCRIPTION - (52-) if 52-106 == 350</t>
   </si>
   <si>
     <t>ChargeItem.service:va-rxpartial</t>
@@ -1309,7 +1317,11 @@
 </t>
   </si>
   <si>
-    <t>2012: reference based on PRESCRIPTION - IB NUMBER &gt; INTEGRATED BILLING ACTION (52-106 &gt; 350-)</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+dpci-27-2012:If 52-106 == 350 then reference /MedicationDispensePartial based on (52-) {true}</t>
+  </si>
+  <si>
+    <t>2012: reference based on PRESCRIPTION - (52-) if 52-106 == 350</t>
   </si>
   <si>
     <t>ChargeItem.product[x]</t>
@@ -7601,10 +7613,10 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>405</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>79</v>
@@ -7624,13 +7636,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>396</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>79</v>
@@ -7652,7 +7664,7 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>398</v>
@@ -7721,10 +7733,10 @@
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>410</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>79</v>
@@ -7744,13 +7756,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>396</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>79</v>
@@ -7772,7 +7784,7 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>398</v>
@@ -7841,10 +7853,10 @@
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>415</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>79</v>
@@ -7864,10 +7876,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7890,13 +7902,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7926,10 +7938,10 @@
         <v>202</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -7947,7 +7959,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7974,7 +7986,7 @@
         <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -7982,10 +7994,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8008,16 +8020,16 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8067,7 +8079,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8102,10 +8114,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8128,13 +8140,13 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8185,7 +8197,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8206,13 +8218,13 @@
         <v>79</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>79</v>
@@ -8220,10 +8232,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8246,13 +8258,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8303,7 +8315,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8324,7 +8336,7 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItemcharges.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -822,7 +822,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpci-27-2008:If 360-1.04 == 350 &amp;&amp; Outpatient then reference /EncounterOutpatient based on (360-1.02 &gt; 399-304&gt;399.0304-20&gt;409.68-.05) {true}dpci-27-2009:If 360-1.04 == 350 &amp;&amp; Inpatient then reference /EncounterInpatientEncounter based on (360-1.02 &gt; 399-.08) {true}</t>
+dpci-27-2008:If 360-1.04 == 350  &amp;&amp; Outpatient then reference /EncounterOutpatient based on (360-1.02 &gt; 399-304&gt;399.0304-20&gt;409.68-.05) {true}dpci-27-2009:If 360-1.04 == 350 &amp;&amp; Inpatient then reference /EncounterInpatientEncounter based on (360-1.02 &gt; 399-.08) {true}</t>
   </si>
   <si>
     <t>2009: reference based on IB-FB INTERFACE TRACKING - BILL/CLAIMS &gt; BILL/CLAIMS - PTF ENTRY NUMBER (360-1.02 &gt; 399-.08) if 360-1.04 == 350 &amp;&amp; Inpatient</t>
